--- a/precios_mcallen_2026-04-23.xlsx
+++ b/precios_mcallen_2026-04-23.xlsx
@@ -595,7 +595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC: $1 USD = $17.32 MXN  |  USDA AMS + SNIIM + Claude  |  23/04/2026 06:17  |  PRECIOS DE REFERENCIA</t>
+          <t>TC: $1 USD = $17.32 MXN  |  USDA AMS + SNIIM + Claude  |  23/04/2026 06:35  |  PRECIOS DE REFERENCIA</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>$21.15</t>
+          <t>$22.73</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>$+16.95</t>
+          <t>$+15.37</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>+80.1%</t>
+          <t>+67.6%</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>$24.07</t>
+          <t>$26.23</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>$+33.26</t>
+          <t>$+31.10</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>+138.2%</t>
+          <t>+118.6%</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>$16.52</t>
+          <t>$16.63</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>$+5.30</t>
+          <t>$+5.19</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>+32.1%</t>
+          <t>+31.2%</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>$21.53</t>
+          <t>$21.71</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>$+12.76</t>
+          <t>$+12.58</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>+59.3%</t>
+          <t>+57.9%</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>$21.61</t>
+          <t>$21.65</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>$+6.97</t>
+          <t>$+6.93</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>+32.3%</t>
+          <t>+32.0%</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>$15.58</t>
+          <t>$15.79</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>$-1.03</t>
+          <t>$-1.24</t>
         </is>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="N12" s="18" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>$11.98</t>
+          <t>$12.70</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>$+6.03</t>
+          <t>$+5.31</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>+50.3%</t>
+          <t>+41.8%</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>$15.88</t>
+          <t>$15.53</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>$+14.60</t>
+          <t>$+14.95</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>+91.9%</t>
+          <t>+96.3%</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$15.79</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>$+7.31</t>
+          <t>$+6.03</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>+50.4%</t>
+          <t>+38.2%</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>$14.38</t>
+          <t>$15.16</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>$+10.39</t>
+          <t>$+9.61</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>+72.3%</t>
+          <t>+63.4%</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>$35.85</t>
+          <t>$37.45</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>$+34.82</t>
+          <t>$+33.22</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>+97.1%</t>
+          <t>+88.7%</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>$33.58</t>
+          <t>$31.54</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>$+31.37</t>
+          <t>$+33.41</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>+93.4%</t>
+          <t>+105.9%</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>$14.52</t>
+          <t>$14.82</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>$+7.30</t>
+          <t>$+7.00</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>+50.3%</t>
+          <t>+47.2%</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>$15.06</t>
+          <t>$15.68</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>$+3.65</t>
+          <t>$+3.03</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>+24.2%</t>
+          <t>+19.3%</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>$9.89</t>
+          <t>$9.92</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>$+2.75</t>
+          <t>$+2.72</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>+27.8%</t>
+          <t>+27.4%</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>$19.16</t>
+          <t>$17.95</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>$+5.61</t>
+          <t>$+6.82</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>+29.3%</t>
+          <t>+38.0%</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>$56.93</t>
+          <t>$57.55</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -2455,19 +2455,19 @@
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="L28" s="7" t="inlineStr">
-        <is>
-          <t>$+0.40</t>
-        </is>
-      </c>
-      <c r="M28" s="7" t="inlineStr">
-        <is>
-          <t>+0.7%</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>Mas barato CDMX</t>
+      <c r="L28" s="17" t="inlineStr">
+        <is>
+          <t>$-0.22</t>
+        </is>
+      </c>
+      <c r="M28" s="17" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="N28" s="18" t="inlineStr">
+        <is>
+          <t>Mas barato McAllen</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>$71.58</t>
+          <t>$68.90</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>$+12.42</t>
+          <t>$+15.10</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>+17.4%</t>
+          <t>+21.9%</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>$12.41</t>
+          <t>$12.24</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>$+2.83</t>
+          <t>$+3.00</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>+22.8%</t>
+          <t>+24.5%</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>$39.80</t>
+          <t>$42.23</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L33" s="17" t="inlineStr">
         <is>
-          <t>$-9.32</t>
+          <t>$-11.75</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="N33" s="18" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>$10.53</t>
+          <t>$9.59</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>$+1.25</t>
+          <t>$+2.19</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>+22.8%</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>$17.44</t>
+          <t>$18.11</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="L35" s="17" t="inlineStr">
         <is>
-          <t>$-0.29</t>
+          <t>$-0.96</t>
         </is>
       </c>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="N35" s="18" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>$12.43</t>
+          <t>$13.01</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>$+4.72</t>
+          <t>$+4.14</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>+38.0%</t>
+          <t>+31.8%</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>$23.62</t>
+          <t>$26.40</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -3103,19 +3103,19 @@
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>$+2.36</t>
-        </is>
-      </c>
-      <c r="M37" s="7" t="inlineStr">
-        <is>
-          <t>+10.0%</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="inlineStr">
-        <is>
-          <t>Mas barato CDMX</t>
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t>$-0.42</t>
+        </is>
+      </c>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="N37" s="18" t="inlineStr">
+        <is>
+          <t>Mas barato McAllen</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>$21.44</t>
+          <t>$20.07</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>$+0.38</t>
+          <t>$+1.75</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+8.7%</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>$42.72</t>
+          <t>$41.14</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>$+5.08</t>
+          <t>$+6.66</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>+16.2%</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>$30.75</t>
+          <t>$31.47</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>$+26.58</t>
+          <t>$+25.86</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>+86.4%</t>
+          <t>+82.2%</t>
         </is>
       </c>
       <c r="N40" s="10" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>$40.68</t>
+          <t>$39.28</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>$+43.32</t>
+          <t>$+44.72</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>+106.5%</t>
+          <t>+113.8%</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>$36.90</t>
+          <t>$38.51</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>$+33.77</t>
+          <t>$+32.16</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>+91.5%</t>
+          <t>+83.5%</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>$12.68</t>
+          <t>$13.11</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>$+7.58</t>
+          <t>$+7.15</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>+59.8%</t>
+          <t>+54.5%</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>$57.17</t>
+          <t>$54.61</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>$+49.69</t>
+          <t>$+52.25</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>+86.9%</t>
+          <t>+95.7%</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
@@ -3698,7 +3698,7 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>Mas barato CDMX: 28  |  Mas barato McAllen: 14</t>
+          <t>Mas barato CDMX: 26  |  Mas barato McAllen: 16</t>
         </is>
       </c>
     </row>

--- a/precios_mcallen_2026-04-23.xlsx
+++ b/precios_mcallen_2026-04-23.xlsx
@@ -595,7 +595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC: $1 USD = $17.32 MXN  |  USDA AMS + SNIIM + Claude  |  23/04/2026 06:35  |  PRECIOS DE REFERENCIA</t>
+          <t>TC: $1 USD = $17.35 MXN  |  USDA AMS + SNIIM + Claude  |  23/04/2026 17:59  |  PRECIOS DE REFERENCIA</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>$38.10</t>
+          <t>$38.17</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>$22.73</t>
+          <t>$23.56</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>$+15.37</t>
+          <t>$+14.61</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>+67.6%</t>
+          <t>+62.0%</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>$57.33</t>
+          <t>$57.43</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>$26.23</t>
+          <t>$25.15</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>$+31.10</t>
+          <t>$+32.28</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>+118.6%</t>
+          <t>+128.3%</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>$21.82</t>
+          <t>$21.86</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>$16.63</t>
+          <t>$16.39</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>$+5.19</t>
+          <t>$+5.47</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>+31.2%</t>
+          <t>+33.4%</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>$34.29</t>
+          <t>$34.35</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>$21.71</t>
+          <t>$20.35</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>$+12.58</t>
+          <t>$+14.00</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>+57.9%</t>
+          <t>+68.8%</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>$25.98</t>
+          <t>$26.03</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t>$-4.02</t>
+          <t>$-3.97</t>
         </is>
       </c>
       <c r="M8" s="17" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="N8" s="18" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>$28.58</t>
+          <t>$28.63</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>$21.65</t>
+          <t>$22.07</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>$+6.93</t>
+          <t>$+6.56</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>+32.0%</t>
+          <t>+29.7%</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>$16.45</t>
+          <t>$16.48</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>$-13.55</t>
+          <t>$-13.52</t>
         </is>
       </c>
       <c r="M10" s="17" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="N10" s="18" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>$11.08</t>
+          <t>$11.10</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>$-16.92</t>
+          <t>$-16.90</t>
         </is>
       </c>
       <c r="M11" s="17" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>$14.55</t>
+          <t>$14.57</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>$15.79</t>
+          <t>$15.16</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>$-1.24</t>
+          <t>$-0.59</t>
         </is>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="N12" s="18" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>$8.83</t>
+          <t>$8.85</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t>$-3.17</t>
+          <t>$-3.15</t>
         </is>
       </c>
       <c r="M13" s="17" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="N13" s="18" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>$18.01</t>
+          <t>$18.04</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>$12.70</t>
+          <t>$11.50</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>$+5.31</t>
+          <t>$+6.54</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>+41.8%</t>
+          <t>+56.9%</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>$30.48</t>
+          <t>$30.54</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>$15.53</t>
+          <t>$16.02</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>$+14.95</t>
+          <t>$+14.52</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>+96.3%</t>
+          <t>+90.6%</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>$21.82</t>
+          <t>$21.86</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>$15.79</t>
+          <t>$15.80</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>$+6.03</t>
+          <t>$+6.06</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>+38.2%</t>
+          <t>+38.4%</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>$24.77</t>
+          <t>$24.81</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>$15.16</t>
+          <t>$15.49</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>$+9.61</t>
+          <t>$+9.32</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>+63.4%</t>
+          <t>+60.2%</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>$15.24</t>
+          <t>$15.27</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L18" s="17" t="inlineStr">
         <is>
-          <t>$-9.76</t>
+          <t>$-9.73</t>
         </is>
       </c>
       <c r="M18" s="17" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="N18" s="18" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>$70.67</t>
+          <t>$70.79</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>$37.45</t>
+          <t>$36.81</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>$+33.22</t>
+          <t>$+33.98</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>+88.7%</t>
+          <t>+92.3%</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>$64.95</t>
+          <t>$65.06</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>$31.54</t>
+          <t>$33.99</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>$+33.41</t>
+          <t>$+31.07</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>+105.9%</t>
+          <t>+91.4%</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>$21.82</t>
+          <t>$21.86</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>$14.82</t>
+          <t>$14.19</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>$+7.00</t>
+          <t>$+7.67</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>+47.2%</t>
+          <t>+54.1%</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>$18.71</t>
+          <t>$18.74</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>$15.68</t>
+          <t>$14.60</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>$+3.03</t>
+          <t>$+4.14</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>+19.3%</t>
+          <t>+28.4%</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>$12.64</t>
+          <t>$12.67</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>$9.92</t>
+          <t>$11.08</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>$+2.72</t>
+          <t>$+1.59</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>+27.4%</t>
+          <t>+14.4%</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>$24.77</t>
+          <t>$24.81</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$17.89</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>$+6.82</t>
+          <t>$+6.92</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>+38.0%</t>
+          <t>+38.7%</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>$26.67</t>
+          <t>$26.72</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L25" s="17" t="inlineStr">
         <is>
-          <t>$-19.33</t>
+          <t>$-19.28</t>
         </is>
       </c>
       <c r="M25" s="17" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="N25" s="18" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>$28.58</t>
+          <t>$28.63</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -2313,12 +2313,12 @@
       </c>
       <c r="L26" s="17" t="inlineStr">
         <is>
-          <t>$-31.42</t>
+          <t>$-31.37</t>
         </is>
       </c>
       <c r="M26" s="17" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-52.3%</t>
         </is>
       </c>
       <c r="N26" s="18" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>$21.82</t>
+          <t>$21.86</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="L27" s="17" t="inlineStr">
         <is>
-          <t>$-13.18</t>
+          <t>$-13.14</t>
         </is>
       </c>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="N27" s="18" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>$57.33</t>
+          <t>$57.43</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>$57.55</t>
+          <t>$57.87</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="L28" s="17" t="inlineStr">
         <is>
-          <t>$-0.22</t>
+          <t>$-0.44</t>
         </is>
       </c>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="N28" s="18" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$84.15</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>$68.90</t>
+          <t>$71.66</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>$+15.10</t>
+          <t>$+12.49</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>+21.9%</t>
+          <t>+17.4%</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>$15.24</t>
+          <t>$15.27</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>$12.24</t>
+          <t>$11.70</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>$+3.00</t>
+          <t>$+3.57</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>+24.5%</t>
+          <t>+30.5%</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>$17.15</t>
+          <t>$17.18</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="L31" s="17" t="inlineStr">
         <is>
-          <t>$-12.85</t>
+          <t>$-12.82</t>
         </is>
       </c>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="N31" s="18" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>$32.39</t>
+          <t>$32.44</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="L32" s="17" t="inlineStr">
         <is>
-          <t>$-12.61</t>
+          <t>$-12.56</t>
         </is>
       </c>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="N32" s="18" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>$30.48</t>
+          <t>$30.54</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>$42.23</t>
+          <t>$40.32</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L33" s="17" t="inlineStr">
         <is>
-          <t>$-11.75</t>
+          <t>$-9.78</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="N33" s="18" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>$11.78</t>
+          <t>$11.80</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>$9.59</t>
+          <t>$9.50</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>$+2.19</t>
+          <t>$+2.30</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>+22.8%</t>
+          <t>+24.2%</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>$17.15</t>
+          <t>$17.18</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>$18.11</t>
+          <t>$17.38</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="L35" s="17" t="inlineStr">
         <is>
-          <t>$-0.96</t>
+          <t>$-0.20</t>
         </is>
       </c>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="N35" s="18" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>$17.15</t>
+          <t>$17.18</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>$13.01</t>
+          <t>$13.54</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>$+4.14</t>
+          <t>$+3.64</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>+31.8%</t>
+          <t>+26.9%</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>$25.98</t>
+          <t>$26.03</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>$26.40</t>
+          <t>$25.77</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -3103,19 +3103,19 @@
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="L37" s="17" t="inlineStr">
-        <is>
-          <t>$-0.42</t>
-        </is>
-      </c>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>-1.6%</t>
-        </is>
-      </c>
-      <c r="N37" s="18" t="inlineStr">
-        <is>
-          <t>Mas barato McAllen</t>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>$+0.26</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>Mas barato CDMX</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>$21.82</t>
+          <t>$21.86</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>$20.07</t>
+          <t>$21.08</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>$+1.75</t>
+          <t>$+0.78</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>+8.7%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>$47.80</t>
+          <t>$47.89</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>$41.14</t>
+          <t>$43.14</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>$+6.66</t>
+          <t>$+4.75</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+11.0%</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>$57.33</t>
+          <t>$57.43</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>$31.47</t>
+          <t>$30.08</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>$+25.86</t>
+          <t>$+27.35</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>+82.2%</t>
+          <t>+90.9%</t>
         </is>
       </c>
       <c r="N40" s="10" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$84.15</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>$39.28</t>
+          <t>$42.75</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>$+44.72</t>
+          <t>$+41.40</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>+113.8%</t>
+          <t>+96.8%</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>$70.67</t>
+          <t>$70.79</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>$38.51</t>
+          <t>$36.08</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>$+32.16</t>
+          <t>$+34.71</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>+83.5%</t>
+          <t>+96.2%</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>$20.26</t>
+          <t>$20.30</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>$13.11</t>
+          <t>$13.12</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>$+7.15</t>
+          <t>$+7.18</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>+54.5%</t>
+          <t>+54.7%</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>$106.86</t>
+          <t>$107.05</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>$54.61</t>
+          <t>$56.17</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>$+52.25</t>
+          <t>$+50.88</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>+95.7%</t>
+          <t>+90.6%</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>$14.90</t>
+          <t>$14.92</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="L45" s="17" t="inlineStr">
         <is>
-          <t>$-35.10</t>
+          <t>$-35.08</t>
         </is>
       </c>
       <c r="M45" s="17" t="inlineStr">
@@ -3698,7 +3698,7 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>Mas barato CDMX: 26  |  Mas barato McAllen: 16</t>
+          <t>Mas barato CDMX: 27  |  Mas barato McAllen: 15</t>
         </is>
       </c>
     </row>
@@ -3879,37 +3879,37 @@
       </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
-          <t>$38.18</t>
+          <t>$38.25</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t>$38.18</t>
+          <t>$38.25</t>
         </is>
       </c>
       <c r="K3" s="21" t="inlineStr">
         <is>
-          <t>$38.18</t>
+          <t>$38.25</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t>$37.80</t>
+          <t>$37.87</t>
         </is>
       </c>
       <c r="M3" s="21" t="inlineStr">
         <is>
-          <t>$38.57</t>
+          <t>$38.63</t>
         </is>
       </c>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t>$37.80</t>
+          <t>$37.87</t>
         </is>
       </c>
       <c r="O3" s="21" t="inlineStr">
         <is>
-          <t>$38.57</t>
+          <t>$38.63</t>
         </is>
       </c>
     </row>
@@ -3956,37 +3956,37 @@
       </c>
       <c r="I4" s="22" t="inlineStr">
         <is>
-          <t>$57.28</t>
+          <t>$57.38</t>
         </is>
       </c>
       <c r="J4" s="22" t="inlineStr">
         <is>
-          <t>$57.28</t>
+          <t>$57.38</t>
         </is>
       </c>
       <c r="K4" s="22" t="inlineStr">
         <is>
-          <t>$57.66</t>
+          <t>$57.76</t>
         </is>
       </c>
       <c r="L4" s="22" t="inlineStr">
         <is>
-          <t>$56.89</t>
+          <t>$56.99</t>
         </is>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
-          <t>$57.66</t>
+          <t>$57.76</t>
         </is>
       </c>
       <c r="N4" s="22" t="inlineStr">
         <is>
-          <t>$56.89</t>
+          <t>$56.99</t>
         </is>
       </c>
       <c r="O4" s="22" t="inlineStr">
         <is>
-          <t>$58.04</t>
+          <t>$58.14</t>
         </is>
       </c>
     </row>
@@ -4033,37 +4033,37 @@
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t>$21.38</t>
+          <t>$21.42</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
-          <t>$22.15</t>
+          <t>$22.19</t>
         </is>
       </c>
     </row>
@@ -4110,37 +4110,37 @@
       </c>
       <c r="I6" s="22" t="inlineStr">
         <is>
-          <t>$34.37</t>
+          <t>$34.43</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>$34.37</t>
+          <t>$34.43</t>
         </is>
       </c>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>$34.37</t>
+          <t>$34.43</t>
         </is>
       </c>
       <c r="L6" s="22" t="inlineStr">
         <is>
-          <t>$33.98</t>
+          <t>$34.04</t>
         </is>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
-          <t>$34.75</t>
+          <t>$34.81</t>
         </is>
       </c>
       <c r="N6" s="22" t="inlineStr">
         <is>
-          <t>$33.98</t>
+          <t>$34.04</t>
         </is>
       </c>
       <c r="O6" s="22" t="inlineStr">
         <is>
-          <t>$34.75</t>
+          <t>$34.81</t>
         </is>
       </c>
     </row>
@@ -4187,37 +4187,37 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
         <is>
-          <t>$26.35</t>
+          <t>$26.39</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t>$25.58</t>
+          <t>$25.63</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
         <is>
-          <t>$26.35</t>
+          <t>$26.39</t>
         </is>
       </c>
     </row>
@@ -4264,37 +4264,37 @@
       </c>
       <c r="I8" s="22" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="J8" s="22" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="L8" s="22" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
-          <t>$29.02</t>
+          <t>$29.07</t>
         </is>
       </c>
       <c r="N8" s="22" t="inlineStr">
         <is>
-          <t>$28.26</t>
+          <t>$28.31</t>
         </is>
       </c>
       <c r="O8" s="22" t="inlineStr">
         <is>
-          <t>$29.02</t>
+          <t>$29.07</t>
         </is>
       </c>
     </row>
@@ -4341,37 +4341,37 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>$16.42</t>
+          <t>$16.45</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>$16.42</t>
+          <t>$16.45</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
         <is>
-          <t>$16.42</t>
+          <t>$16.45</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t>$16.42</t>
+          <t>$16.45</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
         <is>
-          <t>$16.42</t>
+          <t>$16.45</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t>$16.04</t>
+          <t>$16.07</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
         <is>
-          <t>$16.80</t>
+          <t>$16.83</t>
         </is>
       </c>
     </row>
@@ -4418,37 +4418,37 @@
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>$11.07</t>
+          <t>$11.09</t>
         </is>
       </c>
       <c r="J10" s="22" t="inlineStr">
         <is>
-          <t>$11.07</t>
+          <t>$11.09</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>$11.07</t>
+          <t>$11.09</t>
         </is>
       </c>
       <c r="L10" s="22" t="inlineStr">
         <is>
-          <t>$11.07</t>
+          <t>$11.09</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
         <is>
-          <t>$11.07</t>
+          <t>$11.09</t>
         </is>
       </c>
       <c r="N10" s="22" t="inlineStr">
         <is>
-          <t>$11.07</t>
+          <t>$11.09</t>
         </is>
       </c>
       <c r="O10" s="22" t="inlineStr">
         <is>
-          <t>$11.46</t>
+          <t>$11.48</t>
         </is>
       </c>
     </row>
@@ -4495,37 +4495,37 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
         <is>
-          <t>$14.89</t>
+          <t>$14.92</t>
         </is>
       </c>
     </row>
@@ -4572,37 +4572,37 @@
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
       <c r="J12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
       <c r="L12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
       <c r="M12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
       <c r="N12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
       <c r="O12" s="22" t="inlineStr">
         <is>
-          <t>$8.78</t>
+          <t>$8.80</t>
         </is>
       </c>
     </row>
@@ -4649,37 +4649,37 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$17.98</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$17.98</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$17.98</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$17.98</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
         <is>
-          <t>$17.95</t>
+          <t>$17.98</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t>$17.56</t>
+          <t>$17.60</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
         <is>
-          <t>$18.33</t>
+          <t>$18.36</t>
         </is>
       </c>
     </row>
@@ -4726,37 +4726,37 @@
       </c>
       <c r="I14" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="L14" s="22" t="inlineStr">
         <is>
-          <t>$30.17</t>
+          <t>$30.22</t>
         </is>
       </c>
       <c r="M14" s="22" t="inlineStr">
         <is>
-          <t>$30.93</t>
+          <t>$30.98</t>
         </is>
       </c>
       <c r="N14" s="22" t="inlineStr">
         <is>
-          <t>$30.17</t>
+          <t>$30.22</t>
         </is>
       </c>
       <c r="O14" s="22" t="inlineStr">
         <is>
-          <t>$30.93</t>
+          <t>$30.98</t>
         </is>
       </c>
     </row>
@@ -4803,37 +4803,37 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t>$21.38</t>
+          <t>$21.42</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
         <is>
-          <t>$22.15</t>
+          <t>$22.19</t>
         </is>
       </c>
     </row>
@@ -4880,37 +4880,37 @@
       </c>
       <c r="I16" s="22" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
         <is>
-          <t>$25.20</t>
+          <t>$25.25</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
         <is>
-          <t>$24.44</t>
+          <t>$24.48</t>
         </is>
       </c>
       <c r="O16" s="22" t="inlineStr">
         <is>
-          <t>$25.20</t>
+          <t>$25.25</t>
         </is>
       </c>
     </row>
@@ -4957,37 +4957,37 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
         <is>
-          <t>$15.66</t>
+          <t>$15.68</t>
         </is>
       </c>
     </row>
@@ -5034,37 +5034,37 @@
       </c>
       <c r="I18" s="22" t="inlineStr">
         <is>
-          <t>$70.64</t>
+          <t>$70.76</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
         <is>
-          <t>$70.64</t>
+          <t>$70.76</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>$71.02</t>
+          <t>$71.15</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
         <is>
-          <t>$70.26</t>
+          <t>$70.38</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
         <is>
-          <t>$71.02</t>
+          <t>$71.15</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
         <is>
-          <t>$69.88</t>
+          <t>$70.00</t>
         </is>
       </c>
       <c r="O18" s="22" t="inlineStr">
         <is>
-          <t>$71.40</t>
+          <t>$71.53</t>
         </is>
       </c>
     </row>
@@ -5111,37 +5111,37 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>$64.91</t>
+          <t>$65.03</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>$64.91</t>
+          <t>$65.03</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
         <is>
-          <t>$65.29</t>
+          <t>$65.41</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
-          <t>$64.53</t>
+          <t>$64.64</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
         <is>
-          <t>$65.29</t>
+          <t>$65.41</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
         <is>
-          <t>$64.53</t>
+          <t>$64.64</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
         <is>
-          <t>$65.68</t>
+          <t>$65.79</t>
         </is>
       </c>
     </row>
@@ -5188,37 +5188,37 @@
       </c>
       <c r="I20" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
         <is>
-          <t>$21.38</t>
+          <t>$21.42</t>
         </is>
       </c>
       <c r="O20" s="22" t="inlineStr">
         <is>
-          <t>$22.15</t>
+          <t>$22.19</t>
         </is>
       </c>
     </row>
@@ -5265,37 +5265,37 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>$18.71</t>
+          <t>$18.74</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t>$18.71</t>
+          <t>$18.74</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
         <is>
-          <t>$18.71</t>
+          <t>$18.74</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
         <is>
-          <t>$18.71</t>
+          <t>$18.74</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
         <is>
-          <t>$18.71</t>
+          <t>$18.74</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
         <is>
-          <t>$18.33</t>
+          <t>$18.36</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
         <is>
-          <t>$19.09</t>
+          <t>$19.13</t>
         </is>
       </c>
     </row>
@@ -5342,37 +5342,37 @@
       </c>
       <c r="I22" s="22" t="inlineStr">
         <is>
-          <t>$12.60</t>
+          <t>$12.62</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
         <is>
-          <t>$12.60</t>
+          <t>$12.62</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
         <is>
-          <t>$12.60</t>
+          <t>$12.62</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
         <is>
-          <t>$12.60</t>
+          <t>$12.62</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
         <is>
-          <t>$12.60</t>
+          <t>$12.62</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
         <is>
-          <t>$12.60</t>
+          <t>$12.62</t>
         </is>
       </c>
       <c r="O22" s="22" t="inlineStr">
         <is>
-          <t>$12.98</t>
+          <t>$13.01</t>
         </is>
       </c>
     </row>
@@ -5419,37 +5419,37 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t>$24.82</t>
+          <t>$24.86</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
         <is>
-          <t>$25.20</t>
+          <t>$25.25</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
         <is>
-          <t>$24.44</t>
+          <t>$24.48</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
         <is>
-          <t>$25.20</t>
+          <t>$25.25</t>
         </is>
       </c>
     </row>
@@ -5496,37 +5496,37 @@
       </c>
       <c r="I24" s="22" t="inlineStr">
         <is>
-          <t>$26.73</t>
+          <t>$26.78</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
         <is>
-          <t>$26.73</t>
+          <t>$26.78</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
         <is>
-          <t>$26.73</t>
+          <t>$26.78</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
         <is>
-          <t>$26.73</t>
+          <t>$26.78</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
         <is>
-          <t>$27.11</t>
+          <t>$27.16</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
         <is>
-          <t>$26.35</t>
+          <t>$26.39</t>
         </is>
       </c>
       <c r="O24" s="22" t="inlineStr">
         <is>
-          <t>$27.11</t>
+          <t>$27.16</t>
         </is>
       </c>
     </row>
@@ -5573,37 +5573,37 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
         <is>
-          <t>$28.64</t>
+          <t>$28.69</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
         <is>
-          <t>$29.02</t>
+          <t>$29.07</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
         <is>
-          <t>$28.26</t>
+          <t>$28.31</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
         <is>
-          <t>$29.02</t>
+          <t>$29.07</t>
         </is>
       </c>
     </row>
@@ -5650,37 +5650,37 @@
       </c>
       <c r="I26" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
         <is>
-          <t>$21.38</t>
+          <t>$21.42</t>
         </is>
       </c>
       <c r="O26" s="22" t="inlineStr">
         <is>
-          <t>$22.15</t>
+          <t>$22.19</t>
         </is>
       </c>
     </row>
@@ -5727,37 +5727,37 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>$57.28</t>
+          <t>$57.38</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t>$57.28</t>
+          <t>$57.38</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
         <is>
-          <t>$57.66</t>
+          <t>$57.76</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
         <is>
-          <t>$56.89</t>
+          <t>$56.99</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
         <is>
-          <t>$57.66</t>
+          <t>$57.76</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
         <is>
-          <t>$56.89</t>
+          <t>$56.99</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
         <is>
-          <t>$58.04</t>
+          <t>$58.14</t>
         </is>
       </c>
     </row>
@@ -5804,37 +5804,37 @@
       </c>
       <c r="I28" s="22" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$84.15</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$84.15</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
         <is>
-          <t>$84.39</t>
+          <t>$84.53</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
         <is>
-          <t>$83.62</t>
+          <t>$83.77</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>$84.77</t>
+          <t>$84.92</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
         <is>
-          <t>$83.24</t>
+          <t>$83.39</t>
         </is>
       </c>
       <c r="O28" s="22" t="inlineStr">
         <is>
-          <t>$84.77</t>
+          <t>$84.92</t>
         </is>
       </c>
     </row>
@@ -5881,37 +5881,37 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
         <is>
-          <t>$15.66</t>
+          <t>$15.68</t>
         </is>
       </c>
     </row>
@@ -5958,37 +5958,37 @@
       </c>
       <c r="I30" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="N30" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="O30" s="22" t="inlineStr">
         <is>
-          <t>$17.56</t>
+          <t>$17.60</t>
         </is>
       </c>
     </row>
@@ -6035,37 +6035,37 @@
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
-          <t>$32.46</t>
+          <t>$32.51</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t>$32.46</t>
+          <t>$32.51</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
         <is>
-          <t>$32.46</t>
+          <t>$32.51</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
         <is>
-          <t>$32.46</t>
+          <t>$32.51</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
         <is>
-          <t>$32.84</t>
+          <t>$32.90</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
         <is>
-          <t>$32.07</t>
+          <t>$32.13</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
         <is>
-          <t>$32.84</t>
+          <t>$32.90</t>
         </is>
       </c>
     </row>
@@ -6112,37 +6112,37 @@
       </c>
       <c r="I32" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
         <is>
-          <t>$30.55</t>
+          <t>$30.60</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
         <is>
-          <t>$30.93</t>
+          <t>$30.98</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr">
         <is>
-          <t>$30.17</t>
+          <t>$30.22</t>
         </is>
       </c>
       <c r="O32" s="22" t="inlineStr">
         <is>
-          <t>$30.93</t>
+          <t>$30.98</t>
         </is>
       </c>
     </row>
@@ -6189,37 +6189,37 @@
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>$11.84</t>
+          <t>$11.86</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>$11.84</t>
+          <t>$11.86</t>
         </is>
       </c>
       <c r="K33" s="21" t="inlineStr">
         <is>
-          <t>$11.84</t>
+          <t>$11.86</t>
         </is>
       </c>
       <c r="L33" s="21" t="inlineStr">
         <is>
-          <t>$11.84</t>
+          <t>$11.86</t>
         </is>
       </c>
       <c r="M33" s="21" t="inlineStr">
         <is>
-          <t>$11.84</t>
+          <t>$11.86</t>
         </is>
       </c>
       <c r="N33" s="21" t="inlineStr">
         <is>
-          <t>$11.84</t>
+          <t>$11.86</t>
         </is>
       </c>
       <c r="O33" s="21" t="inlineStr">
         <is>
-          <t>$12.22</t>
+          <t>$12.24</t>
         </is>
       </c>
     </row>
@@ -6266,37 +6266,37 @@
       </c>
       <c r="I34" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="N34" s="22" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="O34" s="22" t="inlineStr">
         <is>
-          <t>$17.56</t>
+          <t>$17.60</t>
         </is>
       </c>
     </row>
@@ -6343,37 +6343,37 @@
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="J35" s="21" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="K35" s="21" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="L35" s="21" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="M35" s="21" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="N35" s="21" t="inlineStr">
         <is>
-          <t>$17.18</t>
+          <t>$17.21</t>
         </is>
       </c>
       <c r="O35" s="21" t="inlineStr">
         <is>
-          <t>$17.56</t>
+          <t>$17.60</t>
         </is>
       </c>
     </row>
@@ -6420,37 +6420,37 @@
       </c>
       <c r="I36" s="22" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
         <is>
-          <t>$25.97</t>
+          <t>$26.01</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
         <is>
-          <t>$26.35</t>
+          <t>$26.39</t>
         </is>
       </c>
       <c r="N36" s="22" t="inlineStr">
         <is>
-          <t>$25.58</t>
+          <t>$25.63</t>
         </is>
       </c>
       <c r="O36" s="22" t="inlineStr">
         <is>
-          <t>$26.35</t>
+          <t>$26.39</t>
         </is>
       </c>
     </row>
@@ -6497,37 +6497,37 @@
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="K37" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="L37" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="M37" s="21" t="inlineStr">
         <is>
-          <t>$21.76</t>
+          <t>$21.80</t>
         </is>
       </c>
       <c r="N37" s="21" t="inlineStr">
         <is>
-          <t>$21.38</t>
+          <t>$21.42</t>
         </is>
       </c>
       <c r="O37" s="21" t="inlineStr">
         <is>
-          <t>$22.15</t>
+          <t>$22.19</t>
         </is>
       </c>
     </row>
@@ -6574,37 +6574,37 @@
       </c>
       <c r="I38" s="22" t="inlineStr">
         <is>
-          <t>$47.73</t>
+          <t>$47.81</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
         <is>
-          <t>$47.73</t>
+          <t>$47.81</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
         <is>
-          <t>$47.73</t>
+          <t>$47.81</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr">
         <is>
-          <t>$47.35</t>
+          <t>$47.43</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
         <is>
-          <t>$48.11</t>
+          <t>$48.20</t>
         </is>
       </c>
       <c r="N38" s="22" t="inlineStr">
         <is>
-          <t>$47.35</t>
+          <t>$47.43</t>
         </is>
       </c>
       <c r="O38" s="22" t="inlineStr">
         <is>
-          <t>$48.11</t>
+          <t>$48.20</t>
         </is>
       </c>
     </row>
@@ -6651,37 +6651,37 @@
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
-          <t>$57.28</t>
+          <t>$57.38</t>
         </is>
       </c>
       <c r="J39" s="21" t="inlineStr">
         <is>
-          <t>$57.28</t>
+          <t>$57.38</t>
         </is>
       </c>
       <c r="K39" s="21" t="inlineStr">
         <is>
-          <t>$57.66</t>
+          <t>$57.76</t>
         </is>
       </c>
       <c r="L39" s="21" t="inlineStr">
         <is>
-          <t>$56.89</t>
+          <t>$56.99</t>
         </is>
       </c>
       <c r="M39" s="21" t="inlineStr">
         <is>
-          <t>$57.66</t>
+          <t>$57.76</t>
         </is>
       </c>
       <c r="N39" s="21" t="inlineStr">
         <is>
-          <t>$56.89</t>
+          <t>$56.99</t>
         </is>
       </c>
       <c r="O39" s="21" t="inlineStr">
         <is>
-          <t>$58.04</t>
+          <t>$58.14</t>
         </is>
       </c>
     </row>
@@ -6728,37 +6728,37 @@
       </c>
       <c r="I40" s="22" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$84.15</t>
         </is>
       </c>
       <c r="J40" s="22" t="inlineStr">
         <is>
-          <t>$84.00</t>
+          <t>$84.15</t>
         </is>
       </c>
       <c r="K40" s="22" t="inlineStr">
         <is>
-          <t>$84.39</t>
+          <t>$84.53</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr">
         <is>
-          <t>$83.62</t>
+          <t>$83.77</t>
         </is>
       </c>
       <c r="M40" s="22" t="inlineStr">
         <is>
-          <t>$84.77</t>
+          <t>$84.92</t>
         </is>
       </c>
       <c r="N40" s="22" t="inlineStr">
         <is>
-          <t>$83.24</t>
+          <t>$83.39</t>
         </is>
       </c>
       <c r="O40" s="22" t="inlineStr">
         <is>
-          <t>$84.77</t>
+          <t>$84.92</t>
         </is>
       </c>
     </row>
@@ -6805,37 +6805,37 @@
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
-          <t>$70.64</t>
+          <t>$70.76</t>
         </is>
       </c>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t>$70.64</t>
+          <t>$70.76</t>
         </is>
       </c>
       <c r="K41" s="21" t="inlineStr">
         <is>
-          <t>$71.02</t>
+          <t>$71.15</t>
         </is>
       </c>
       <c r="L41" s="21" t="inlineStr">
         <is>
-          <t>$70.26</t>
+          <t>$70.38</t>
         </is>
       </c>
       <c r="M41" s="21" t="inlineStr">
         <is>
-          <t>$71.02</t>
+          <t>$71.15</t>
         </is>
       </c>
       <c r="N41" s="21" t="inlineStr">
         <is>
-          <t>$69.88</t>
+          <t>$70.00</t>
         </is>
       </c>
       <c r="O41" s="21" t="inlineStr">
         <is>
-          <t>$71.40</t>
+          <t>$71.53</t>
         </is>
       </c>
     </row>
@@ -6882,37 +6882,37 @@
       </c>
       <c r="I42" s="22" t="inlineStr">
         <is>
-          <t>$20.24</t>
+          <t>$20.27</t>
         </is>
       </c>
       <c r="J42" s="22" t="inlineStr">
         <is>
-          <t>$20.24</t>
+          <t>$20.27</t>
         </is>
       </c>
       <c r="K42" s="22" t="inlineStr">
         <is>
-          <t>$20.24</t>
+          <t>$20.27</t>
         </is>
       </c>
       <c r="L42" s="22" t="inlineStr">
         <is>
-          <t>$20.24</t>
+          <t>$20.27</t>
         </is>
       </c>
       <c r="M42" s="22" t="inlineStr">
         <is>
-          <t>$20.62</t>
+          <t>$20.66</t>
         </is>
       </c>
       <c r="N42" s="22" t="inlineStr">
         <is>
-          <t>$19.86</t>
+          <t>$19.89</t>
         </is>
       </c>
       <c r="O42" s="22" t="inlineStr">
         <is>
-          <t>$20.62</t>
+          <t>$20.66</t>
         </is>
       </c>
     </row>
@@ -6959,37 +6959,37 @@
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
-          <t>$106.92</t>
+          <t>$107.10</t>
         </is>
       </c>
       <c r="J43" s="21" t="inlineStr">
         <is>
-          <t>$106.53</t>
+          <t>$106.72</t>
         </is>
       </c>
       <c r="K43" s="21" t="inlineStr">
         <is>
-          <t>$107.30</t>
+          <t>$107.48</t>
         </is>
       </c>
       <c r="L43" s="21" t="inlineStr">
         <is>
-          <t>$106.15</t>
+          <t>$106.34</t>
         </is>
       </c>
       <c r="M43" s="21" t="inlineStr">
         <is>
-          <t>$107.68</t>
+          <t>$107.87</t>
         </is>
       </c>
       <c r="N43" s="21" t="inlineStr">
         <is>
-          <t>$105.77</t>
+          <t>$105.95</t>
         </is>
       </c>
       <c r="O43" s="21" t="inlineStr">
         <is>
-          <t>$108.44</t>
+          <t>$108.63</t>
         </is>
       </c>
     </row>
@@ -7036,37 +7036,37 @@
       </c>
       <c r="I44" s="22" t="inlineStr">
         <is>
-          <t>$14.89</t>
+          <t>$14.92</t>
         </is>
       </c>
       <c r="J44" s="22" t="inlineStr">
         <is>
-          <t>$14.89</t>
+          <t>$14.92</t>
         </is>
       </c>
       <c r="K44" s="22" t="inlineStr">
         <is>
-          <t>$14.89</t>
+          <t>$14.92</t>
         </is>
       </c>
       <c r="L44" s="22" t="inlineStr">
         <is>
-          <t>$14.89</t>
+          <t>$14.92</t>
         </is>
       </c>
       <c r="M44" s="22" t="inlineStr">
         <is>
-          <t>$14.89</t>
+          <t>$14.92</t>
         </is>
       </c>
       <c r="N44" s="22" t="inlineStr">
         <is>
-          <t>$14.51</t>
+          <t>$14.54</t>
         </is>
       </c>
       <c r="O44" s="22" t="inlineStr">
         <is>
-          <t>$15.27</t>
+          <t>$15.30</t>
         </is>
       </c>
     </row>

--- a/precios_mcallen_2026-04-23.xlsx
+++ b/precios_mcallen_2026-04-23.xlsx
@@ -595,7 +595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TC: $1 USD = $17.35 MXN  |  USDA AMS + SNIIM + Claude  |  23/04/2026 17:59  |  PRECIOS DE REFERENCIA</t>
+          <t>TC: $1 USD = $17.35 MXN  |  USDA AMS + SNIIM + Claude  |  23/04/2026 22:49  |  PRECIOS DE REFERENCIA</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>$23.56</t>
+          <t>$23.62</t>
         </is>
       </c>
       <c r="J4" s="9" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>$+14.61</t>
+          <t>$+14.55</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
         <is>
-          <t>+62.0%</t>
+          <t>+61.6%</t>
         </is>
       </c>
       <c r="N4" s="10" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>$25.15</t>
+          <t>$23.84</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>$+32.28</t>
+          <t>$+33.59</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>+128.3%</t>
+          <t>+140.9%</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>$16.39</t>
+          <t>$17.18</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>$+5.47</t>
+          <t>$+4.68</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>+33.4%</t>
+          <t>+27.2%</t>
         </is>
       </c>
       <c r="N6" s="10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>$20.35</t>
+          <t>$22.72</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>$+14.00</t>
+          <t>$+11.63</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>+68.8%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>$22.07</t>
+          <t>$21.47</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>$+6.56</t>
+          <t>$+7.16</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
         <is>
-          <t>+29.7%</t>
+          <t>+33.3%</t>
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>$15.16</t>
+          <t>$14.74</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>$-0.59</t>
+          <t>$-0.17</t>
         </is>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="N12" s="18" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>$11.50</t>
+          <t>$12.15</t>
         </is>
       </c>
       <c r="J14" s="9" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>$+6.54</t>
+          <t>$+5.89</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
         <is>
-          <t>+56.9%</t>
+          <t>+48.5%</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>$16.02</t>
+          <t>$16.33</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>$+14.52</t>
+          <t>$+14.21</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
         <is>
-          <t>+90.6%</t>
+          <t>+87.0%</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>$15.80</t>
+          <t>$14.16</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>$+6.06</t>
+          <t>$+7.70</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>+38.4%</t>
+          <t>+54.4%</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>$15.49</t>
+          <t>$14.13</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>$+9.32</t>
+          <t>$+10.68</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>+60.2%</t>
+          <t>+75.6%</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>$36.81</t>
+          <t>$38.43</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>$+33.98</t>
+          <t>$+32.36</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
         <is>
-          <t>+92.3%</t>
+          <t>+84.2%</t>
         </is>
       </c>
       <c r="N19" s="10" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>$33.99</t>
+          <t>$32.27</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>$+31.07</t>
+          <t>$+32.79</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>+91.4%</t>
+          <t>+101.6%</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>$14.19</t>
+          <t>$14.28</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>$+7.67</t>
+          <t>$+7.58</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>+54.1%</t>
+          <t>+53.1%</t>
         </is>
       </c>
       <c r="N21" s="10" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>$14.60</t>
+          <t>$15.17</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>$+4.14</t>
+          <t>$+3.57</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>+28.4%</t>
+          <t>+23.5%</t>
         </is>
       </c>
       <c r="N22" s="10" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="I23" s="15" t="inlineStr">
         <is>
-          <t>$11.08</t>
+          <t>$10.18</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>$+1.59</t>
+          <t>$+2.49</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>+24.5%</t>
         </is>
       </c>
       <c r="N23" s="10" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>$17.89</t>
+          <t>$18.99</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>$+6.92</t>
+          <t>$+5.82</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>+38.7%</t>
+          <t>+30.6%</t>
         </is>
       </c>
       <c r="N24" s="10" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>$57.87</t>
+          <t>$52.58</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -2455,19 +2455,19 @@
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>$-0.44</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="N28" s="18" t="inlineStr">
-        <is>
-          <t>Mas barato McAllen</t>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>$+4.85</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>+9.2%</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>Mas barato CDMX</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>$71.66</t>
+          <t>$67.58</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>$+12.49</t>
+          <t>$+16.57</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
         <is>
-          <t>+17.4%</t>
+          <t>+24.5%</t>
         </is>
       </c>
       <c r="N29" s="10" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>$11.70</t>
+          <t>$12.00</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>$+3.57</t>
+          <t>$+3.27</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>+30.5%</t>
+          <t>+27.3%</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>$40.32</t>
+          <t>$39.09</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L33" s="17" t="inlineStr">
         <is>
-          <t>$-9.78</t>
+          <t>$-8.55</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="N33" s="18" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>$9.50</t>
+          <t>$10.41</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>$+2.30</t>
+          <t>$+1.39</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
         <is>
-          <t>+24.2%</t>
+          <t>+13.4%</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>$17.38</t>
+          <t>$17.15</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
@@ -2959,19 +2959,19 @@
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="L35" s="17" t="inlineStr">
-        <is>
-          <t>$-0.20</t>
-        </is>
-      </c>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
-      <c r="N35" s="18" t="inlineStr">
-        <is>
-          <t>Mas barato McAllen</t>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>$+0.03</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
+        <is>
+          <t>Mas barato CDMX</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>$13.54</t>
+          <t>$12.48</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>$+3.64</t>
+          <t>$+4.70</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
         <is>
-          <t>+26.9%</t>
+          <t>+37.7%</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>$25.77</t>
+          <t>$25.31</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>$+0.26</t>
+          <t>$+0.72</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
         <is>
-          <t>+1.0%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="N37" s="10" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>$21.08</t>
+          <t>$19.98</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>$+0.78</t>
+          <t>$+1.88</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="N38" s="10" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>$43.14</t>
+          <t>$39.17</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>$+4.75</t>
+          <t>$+8.72</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+22.3%</t>
         </is>
       </c>
       <c r="N39" s="10" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>$30.08</t>
+          <t>$30.98</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>$+27.35</t>
+          <t>$+26.45</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>+90.9%</t>
+          <t>+85.4%</t>
         </is>
       </c>
       <c r="N40" s="10" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>$42.75</t>
+          <t>$43.28</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>$+41.40</t>
+          <t>$+40.87</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>+96.8%</t>
+          <t>+94.4%</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>$36.08</t>
+          <t>$37.93</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>$+34.71</t>
+          <t>$+32.86</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>+96.2%</t>
+          <t>+86.6%</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>$13.12</t>
+          <t>$13.33</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>$+7.18</t>
+          <t>$+6.97</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>+54.7%</t>
+          <t>+52.3%</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>$56.17</t>
+          <t>$56.65</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>$+50.88</t>
+          <t>$+50.40</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
         <is>
-          <t>+90.6%</t>
+          <t>+89.0%</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
@@ -3698,7 +3698,7 @@
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>Mas barato CDMX: 27  |  Mas barato McAllen: 15</t>
+          <t>Mas barato CDMX: 29  |  Mas barato McAllen: 13</t>
         </is>
       </c>
     </row>
